--- a/sheets/대금율보/검수/짝사랑.xlsx
+++ b/sheets/대금율보/검수/짝사랑.xlsx
@@ -2514,20 +2514,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -3080,7 +3080,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -3099,7 +3099,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -3124,6 +3124,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>